--- a/artfynd/A 28704-2024 artfynd.xlsx
+++ b/artfynd/A 28704-2024 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>80086162</v>
       </c>
       <c r="B10" t="n">
-        <v>96251</v>
+        <v>98092</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613787.9397484874</v>
+        <v>613788</v>
       </c>
       <c r="R10" t="n">
-        <v>6886245.001329497</v>
+        <v>6886245</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1843,19 +1843,9 @@
           <t>2019-09-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-09-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 28704-2024 artfynd.xlsx
+++ b/artfynd/A 28704-2024 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>80086162</v>
       </c>
       <c r="B10" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 28704-2024 artfynd.xlsx
+++ b/artfynd/A 28704-2024 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>80086162</v>
       </c>
       <c r="B10" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 28704-2024 artfynd.xlsx
+++ b/artfynd/A 28704-2024 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>80086162</v>
       </c>
       <c r="B10" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 28704-2024 artfynd.xlsx
+++ b/artfynd/A 28704-2024 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>80086162</v>
       </c>
       <c r="B10" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1775,11 +1775,6 @@
       </c>
       <c r="E10" t="n">
         <v>219790</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 28704-2024 artfynd.xlsx
+++ b/artfynd/A 28704-2024 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>80086162</v>
       </c>
       <c r="B10" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1775,6 +1775,11 @@
       </c>
       <c r="E10" t="n">
         <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 28704-2024 artfynd.xlsx
+++ b/artfynd/A 28704-2024 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>80086162</v>
       </c>
       <c r="B10" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 28704-2024 artfynd.xlsx
+++ b/artfynd/A 28704-2024 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>80086162</v>
       </c>
       <c r="B10" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 28704-2024 artfynd.xlsx
+++ b/artfynd/A 28704-2024 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>80086162</v>
       </c>
       <c r="B10" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 28704-2024 artfynd.xlsx
+++ b/artfynd/A 28704-2024 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>80086162</v>
       </c>
       <c r="B10" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 28704-2024 artfynd.xlsx
+++ b/artfynd/A 28704-2024 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>80086162</v>
       </c>
       <c r="B10" t="n">
-        <v>98161</v>
+        <v>98264</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
